--- a/Data/Excel/world_reward.xlsx
+++ b/Data/Excel/world_reward.xlsx
@@ -215,13 +215,13 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>200101</v>
+        <v>30920001</v>
       </c>
       <c r="C5">
-        <v>2001</v>
+        <v>30902001</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -235,13 +235,13 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>200201</v>
+        <v>30920002</v>
       </c>
       <c r="C6">
-        <v>2002</v>
+        <v>30902002</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -255,13 +255,13 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>200301</v>
+        <v>30920003</v>
       </c>
       <c r="C7">
-        <v>2003</v>
+        <v>30902003</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>20300001</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -275,13 +275,13 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>200401</v>
+        <v>30920004</v>
       </c>
       <c r="C8">
-        <v>2004</v>
+        <v>30902004</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>20000004</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -295,13 +295,13 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>200501</v>
+        <v>30920005</v>
       </c>
       <c r="C9">
-        <v>2005</v>
+        <v>30902005</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>20000005</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -315,13 +315,13 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>200601</v>
+        <v>30920006</v>
       </c>
       <c r="C10">
-        <v>2006</v>
+        <v>30902006</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>20100003</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -335,13 +335,13 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>200701</v>
+        <v>30920007</v>
       </c>
       <c r="C11">
-        <v>2007</v>
+        <v>30902007</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>20100001</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -355,13 +355,13 @@
     </row>
     <row r="12">
       <c r="B12">
-        <v>200801</v>
+        <v>30920008</v>
       </c>
       <c r="C12">
-        <v>2008</v>
+        <v>30902008</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>20100002</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -375,13 +375,13 @@
     </row>
     <row r="13">
       <c r="B13">
-        <v>210201</v>
+        <v>30920009</v>
       </c>
       <c r="C13">
-        <v>2102</v>
+        <v>30902009</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -395,13 +395,13 @@
     </row>
     <row r="14">
       <c r="B14">
-        <v>210501</v>
+        <v>30920010</v>
       </c>
       <c r="C14">
-        <v>2105</v>
+        <v>30902010</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>20000004</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -415,13 +415,13 @@
     </row>
     <row r="15">
       <c r="B15">
-        <v>210601</v>
+        <v>30920011</v>
       </c>
       <c r="C15">
-        <v>2106</v>
+        <v>30902011</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>20000005</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -435,13 +435,13 @@
     </row>
     <row r="16">
       <c r="B16">
-        <v>210701</v>
+        <v>30920012</v>
       </c>
       <c r="C16">
-        <v>2107</v>
+        <v>30902012</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>20100003</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -455,13 +455,13 @@
     </row>
     <row r="17">
       <c r="B17">
-        <v>210801</v>
+        <v>30920013</v>
       </c>
       <c r="C17">
-        <v>2108</v>
+        <v>30902013</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>20100001</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -475,13 +475,13 @@
     </row>
     <row r="18">
       <c r="B18">
-        <v>211001</v>
+        <v>30920014</v>
       </c>
       <c r="C18">
-        <v>2110</v>
+        <v>30902014</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>20100004</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -495,13 +495,13 @@
     </row>
     <row r="19">
       <c r="B19">
-        <v>220101</v>
+        <v>30920015</v>
       </c>
       <c r="C19">
-        <v>2201</v>
+        <v>30902015</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -515,13 +515,13 @@
     </row>
     <row r="20">
       <c r="B20">
-        <v>220201</v>
+        <v>30920016</v>
       </c>
       <c r="C20">
-        <v>2202</v>
+        <v>30902016</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E20">
         <v>1</v>
